--- a/.doc/DM_MC02.xlsx
+++ b/.doc/DM_MC02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itgz2\Desktop\BetaRobot\.doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E624AFCB-3E69-4B90-9B52-04054DC23172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6AE7C4-E9E0-4BBD-8092-72CBFE167EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B4D8D70D-B443-43A2-9CC2-2DCA036B85B5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="190">
   <si>
     <t>PA10</t>
   </si>
@@ -376,10 +376,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SPI3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CAN1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -662,10 +658,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>P1_IO1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -703,6 +695,34 @@
   </si>
   <si>
     <t>?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPI3与sbus冲突</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加热</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1087,7 +1107,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D70F7D60-81F2-4602-A7E9-8B674FC75614}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1105,16 +1124,16 @@
         <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
         <v>64</v>
       </c>
       <c r="F1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1128,10 +1147,10 @@
         <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1142,10 +1161,10 @@
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1159,10 +1178,10 @@
         <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1173,24 +1192,24 @@
         <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" t="s">
         <v>146</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>147</v>
       </c>
-      <c r="D6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1198,64 +1217,64 @@
         <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" t="s">
         <v>120</v>
       </c>
-      <c r="E7" t="s">
-        <v>121</v>
-      </c>
       <c r="F7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F9" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" t="s">
         <v>151</v>
       </c>
-      <c r="C10" t="s">
-        <v>152</v>
-      </c>
       <c r="D10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1266,10 +1285,10 @@
         <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -1280,10 +1299,10 @@
         <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1297,7 +1316,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1311,35 +1330,35 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>131</v>
       </c>
-      <c r="B15" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" t="s">
         <v>166</v>
       </c>
-      <c r="D15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B16" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" t="s">
-        <v>167</v>
-      </c>
       <c r="D16" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1347,19 +1366,19 @@
         <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F17" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -1367,13 +1386,13 @@
         <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1384,13 +1403,16 @@
         <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>189</v>
       </c>
       <c r="F19" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -1401,10 +1423,10 @@
         <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1415,10 +1437,10 @@
         <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1429,10 +1451,10 @@
         <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1446,7 +1468,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1460,49 +1482,49 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>133</v>
       </c>
-      <c r="B25" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" t="s">
         <v>153</v>
       </c>
-      <c r="D25" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="D26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>134</v>
       </c>
-      <c r="B26" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
         <v>154</v>
       </c>
-      <c r="D26" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" t="s">
-        <v>155</v>
-      </c>
       <c r="D27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -1513,10 +1535,10 @@
         <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -1527,21 +1549,21 @@
         <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1555,13 +1577,13 @@
         <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F31" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -1572,10 +1594,10 @@
         <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -1586,13 +1608,13 @@
         <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F33" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -1600,13 +1622,16 @@
         <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="E34" t="s">
+        <v>185</v>
       </c>
       <c r="F34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1620,10 +1645,10 @@
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F35" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1637,13 +1662,13 @@
         <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>26</v>
       </c>
@@ -1651,16 +1676,19 @@
         <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="E37" t="s">
+        <v>186</v>
       </c>
       <c r="F37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1671,122 +1699,122 @@
         <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>137</v>
       </c>
-      <c r="B39" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
         <v>157</v>
       </c>
-      <c r="D39" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="D40" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>138</v>
       </c>
-      <c r="B40" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" t="s">
         <v>158</v>
       </c>
-      <c r="D40" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="D41" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>139</v>
       </c>
-      <c r="B41" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B42" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" t="s">
         <v>159</v>
       </c>
-      <c r="D41" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="D42" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>140</v>
       </c>
-      <c r="B42" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" t="s">
+        <v>145</v>
+      </c>
+      <c r="C43" t="s">
         <v>160</v>
       </c>
-      <c r="D42" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>141</v>
-      </c>
-      <c r="B43" t="s">
-        <v>146</v>
-      </c>
-      <c r="C43" t="s">
-        <v>161</v>
-      </c>
       <c r="D43" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="C44" t="s">
         <v>81</v>
       </c>
       <c r="D44" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="C45" t="s">
         <v>88</v>
       </c>
       <c r="D45" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="C46" t="s">
         <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>31</v>
       </c>
@@ -1794,19 +1822,19 @@
         <v>82</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F47" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -1814,19 +1842,19 @@
         <v>82</v>
       </c>
       <c r="C48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1834,120 +1862,120 @@
         <v>82</v>
       </c>
       <c r="C49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F49" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>34</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
         <v>76</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
         <v>75</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>36</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
         <v>76</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F52" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C53" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
         <v>94</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>38</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
         <v>75</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s">
         <v>76</v>
       </c>
       <c r="D56" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>40</v>
       </c>
@@ -1958,10 +1986,10 @@
         <v>73</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>41</v>
       </c>
@@ -1972,10 +2000,10 @@
         <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>42</v>
       </c>
@@ -1986,10 +2014,10 @@
         <v>76</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>43</v>
       </c>
@@ -1997,19 +2025,19 @@
         <v>82</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D60" t="s">
+        <v>119</v>
+      </c>
+      <c r="E60" t="s">
         <v>120</v>
       </c>
-      <c r="E60" t="s">
-        <v>121</v>
-      </c>
       <c r="F60" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>44</v>
       </c>
@@ -2017,212 +2045,212 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D61" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C62" t="s">
         <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
         <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>47</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
         <v>76</v>
       </c>
       <c r="D64" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E64" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>48</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C65" t="s">
         <v>75</v>
       </c>
       <c r="D65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E65" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>49</v>
       </c>
       <c r="B66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
         <v>76</v>
       </c>
       <c r="D66" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E66" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
         <v>75</v>
       </c>
       <c r="D67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E67" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C68" t="s">
         <v>76</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>52</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C69" t="s">
         <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>142</v>
+      </c>
+      <c r="B70" t="s">
+        <v>145</v>
+      </c>
+      <c r="C70" t="s">
+        <v>162</v>
+      </c>
+      <c r="D70" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>143</v>
       </c>
-      <c r="B70" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="B71" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" t="s">
         <v>163</v>
       </c>
-      <c r="D70" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="D71" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>144</v>
       </c>
-      <c r="B71" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="B72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72" t="s">
         <v>164</v>
       </c>
-      <c r="D71" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>145</v>
-      </c>
-      <c r="B72" t="s">
-        <v>146</v>
-      </c>
-      <c r="C72" t="s">
-        <v>165</v>
-      </c>
       <c r="D72" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>53</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
         <v>76</v>
       </c>
       <c r="D73" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>54</v>
       </c>
       <c r="B74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C74" t="s">
         <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C75" t="s">
         <v>66</v>
@@ -2231,10 +2259,10 @@
         <v>65</v>
       </c>
       <c r="F75" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>56</v>
       </c>
@@ -2242,19 +2270,19 @@
         <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D76" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F76" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>57</v>
       </c>
@@ -2262,13 +2290,13 @@
         <v>68</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D77" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>58</v>
       </c>
@@ -2276,24 +2304,24 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D78" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="F78" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C79" t="s">
         <v>71</v>
@@ -2302,10 +2330,10 @@
         <v>65</v>
       </c>
       <c r="F79" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>60</v>
       </c>
@@ -2313,19 +2341,19 @@
         <v>82</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D80" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E80" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F80" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>61</v>
       </c>
@@ -2333,20 +2361,13 @@
         <v>86</v>
       </c>
       <c r="C81" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D81" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F81" xr:uid="{D70F7D60-81F2-4602-A7E9-8B674FC75614}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="SPI2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
